--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -11,12 +11,13 @@
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
     <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
     <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
+    <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="121">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -117,24 +118,45 @@
     <t>http://unitsofmeasure.org</t>
   </si>
   <si>
+    <t>DNK05463</t>
+  </si>
+  <si>
+    <t>source-is-broader-than-target</t>
+  </si>
+  <si>
+    <t>mm[Hg]</t>
+  </si>
+  <si>
+    <t>DNK05465</t>
+  </si>
+  <si>
+    <t>DNK05467</t>
+  </si>
+  <si>
+    <t>DNK05469</t>
+  </si>
+  <si>
     <t>DNK05472</t>
   </si>
   <si>
     <t>Blodtryk systolisk;Arm</t>
   </si>
   <si>
-    <t>source-is-broader-than-target</t>
-  </si>
-  <si>
-    <t>mm[Hg]</t>
-  </si>
-  <si>
     <t>DNK05473</t>
   </si>
   <si>
     <t>Blodtryk diastolisk;Arm</t>
   </si>
   <si>
+    <t>NPU02193</t>
+  </si>
+  <si>
+    <t>mmol/L</t>
+  </si>
+  <si>
+    <t>millimole per liter</t>
+  </si>
+  <si>
     <t>NPU03011</t>
   </si>
   <si>
@@ -294,13 +316,19 @@
     <t>MCS88050</t>
   </si>
   <si>
-    <t>Rejse sætte sig testen;Pt</t>
-  </si>
-  <si>
     <t>1/30sec</t>
   </si>
   <si>
     <t>one per 30 seconds</t>
+  </si>
+  <si>
+    <t>MCS88214</t>
+  </si>
+  <si>
+    <t>1/60sec</t>
+  </si>
+  <si>
+    <t>one per 60 seconds</t>
   </si>
   <si>
     <t>http://loinc.org</t>
@@ -613,7 +641,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -654,136 +682,211 @@
       <c r="A3" t="s" s="2">
         <v>33</v>
       </c>
-      <c r="B3" t="s" s="2">
-        <v>34</v>
-      </c>
+      <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D3" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="E3" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>37</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>38</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D4" t="s" s="2">
-        <v>36</v>
-      </c>
       <c r="E4" t="s" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>39</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>40</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D5" t="s" s="2">
-        <v>41</v>
-      </c>
       <c r="E5" t="s" s="2">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>44</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D6" t="s" s="2">
-        <v>45</v>
-      </c>
       <c r="E6" t="s" s="2">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D7" t="s" s="2">
-        <v>49</v>
-      </c>
       <c r="E7" t="s" s="2">
-        <v>50</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="D8" t="s" s="2">
-        <v>53</v>
-      </c>
       <c r="E8" t="s" s="2">
-        <v>54</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>55</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>56</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s" s="2">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s" s="2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="E12" t="s" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>59</v>
       </c>
-      <c r="B10" t="s" s="2">
+      <c r="C13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s" s="2">
         <v>60</v>
       </c>
-      <c r="C10" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s" s="2">
+      <c r="E13" t="s" s="2">
         <v>61</v>
       </c>
-      <c r="E10" t="s" s="2">
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>62</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E14" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="C15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E15" t="s" s="2">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +918,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -832,155 +935,155 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>67</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>73</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E11" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -1012,7 +1115,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1021,7 +1124,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1029,19 +1132,17 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>92</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1051,6 +1152,65 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>103</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -1073,7 +1233,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1090,87 +1250,87 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C4" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E4" t="s" s="2">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="E5" t="s" s="2">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>111</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/fhir/conceptmap-obs-code-to-ucum.xlsx
+++ b/fhir/conceptmap-obs-code-to-ucum.xlsx
@@ -12,12 +12,14 @@
     <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
     <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
     <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
+    <sheet name="Mapping Table 5" r:id="rId9" sheetId="7"/>
+    <sheet name="Mapping Table 6" r:id="rId10" sheetId="8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="130">
   <si>
     <t>Property</t>
   </si>
@@ -34,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -380,6 +382,33 @@
   </si>
   <si>
     <t>cubic centimeter</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.208.176.2.4</t>
+  </si>
+  <si>
+    <t>ZZ5048</t>
+  </si>
+  <si>
+    <t>http://ehealth.sundhed.dk/cs/mds-codes</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-I</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IA</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IB</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-II</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-III</t>
+  </si>
+  <si>
+    <t>MDS-UPDRS-IV</t>
   </si>
 </sst>
 </file>
@@ -1336,4 +1365,197 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>25</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E4" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E5" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E6" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E7" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E8" t="s" s="2">
+        <v>84</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>